--- a/data/processed/impact_links_updated.xlsx
+++ b/data/processed/impact_links_updated.xlsx
@@ -640,8 +640,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M2" s="1" t="n">
-        <v>44333</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2021-05-17</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -706,8 +708,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG2" s="1" t="n">
-        <v>45677</v>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
@@ -757,8 +761,10 @@
           <t>users</t>
         </is>
       </c>
-      <c r="M3" s="1" t="n">
-        <v>44333</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2021-05-17</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -817,8 +823,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG3" s="1" t="n">
-        <v>45677</v>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
@@ -870,8 +878,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>44333</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2021-05-17</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -932,8 +942,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG4" s="1" t="n">
-        <v>45677</v>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
@@ -985,8 +997,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M5" s="1" t="n">
-        <v>44774</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -1047,8 +1061,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG5" s="1" t="n">
-        <v>45677</v>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
@@ -1100,8 +1116,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M6" s="1" t="n">
-        <v>44774</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1166,8 +1184,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG6" s="1" t="n">
-        <v>45677</v>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
@@ -1217,8 +1237,10 @@
           <t>users</t>
         </is>
       </c>
-      <c r="M7" s="1" t="n">
-        <v>45139</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -1277,8 +1299,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG7" s="1" t="n">
-        <v>45677</v>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
@@ -1330,8 +1354,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M8" s="1" t="n">
-        <v>45139</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -1392,8 +1418,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG8" s="1" t="n">
-        <v>45677</v>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
@@ -1445,8 +1473,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M9" s="1" t="n">
-        <v>45292</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1511,8 +1541,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG9" s="1" t="n">
-        <v>45677</v>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
@@ -1564,8 +1596,10 @@
           <t>pp</t>
         </is>
       </c>
-      <c r="M10" s="1" t="n">
-        <v>45292</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1630,8 +1664,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG10" s="1" t="n">
-        <v>45677</v>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
@@ -1683,8 +1719,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M11" s="1" t="n">
-        <v>45502</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1745,8 +1783,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG11" s="1" t="n">
-        <v>45677</v>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
@@ -1798,8 +1838,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M12" s="1" t="n">
-        <v>45957</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1864,8 +1906,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG12" s="1" t="n">
-        <v>45677</v>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr">
@@ -1917,8 +1961,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M13" s="1" t="n">
-        <v>45957</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1983,8 +2029,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG13" s="1" t="n">
-        <v>45677</v>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr">
@@ -2036,8 +2084,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M14" s="1" t="n">
-        <v>46009</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -2102,8 +2152,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG14" s="1" t="n">
-        <v>45677</v>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr">
@@ -2155,8 +2207,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="M15" s="1" t="n">
-        <v>46006</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -2217,8 +2271,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AG15" s="1" t="n">
-        <v>45677</v>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr">
